--- a/corpus/xlsx/level-057/template.xlsx
+++ b/corpus/xlsx/level-057/template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="16">
   <si>
     <r>
       <rPr>
@@ -111,7 +111,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -152,14 +160,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -185,7 +185,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -201,15 +209,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">u</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">st</t>
+      <t xml:space="preserve">us</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">t</t>
     </r>
     <r>
       <rPr>
@@ -241,15 +249,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">r}</t>
     </r>
   </si>
   <si>
@@ -267,7 +267,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -308,14 +316,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -341,7 +341,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -390,14 +398,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -423,7 +423,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -479,15 +487,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -505,7 +505,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -561,15 +569,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">l}</t>
     </r>
   </si>
   <si>
@@ -763,39 +763,31 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">#e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ac</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">h i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">te</t>
+      <t xml:space="preserve">{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e</t>
     </r>
     <r>
       <rPr>
@@ -811,15 +803,23 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">}}{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{n</t>
+      <t xml:space="preserve">[i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.n</t>
     </r>
     <r>
       <rPr>
@@ -835,7 +835,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">e}}</t>
+      <t xml:space="preserve">e}</t>
     </r>
   </si>
   <si>
@@ -845,31 +845,55 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">q</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">u</t>
+      <t xml:space="preserve">{d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">te</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">[i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">].</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">qu</t>
     </r>
     <r>
       <rPr>
@@ -885,39 +909,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">y</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">ti</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ty}</t>
     </r>
   </si>
   <si>
@@ -935,6 +935,80 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">em</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">s[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">].</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">pr</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ic</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
       <t xml:space="preserve">{</t>
     </r>
     <r>
@@ -943,55 +1017,71 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">p</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">c</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">em</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">s[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">i+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">1]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.n</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">am</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e}</t>
     </r>
   </si>
   <si>
@@ -1135,7 +1225,7 @@
     <xdr:ext cx="914400" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:red}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1166,7 +1256,7 @@
     <xdr:ext cx="960120" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1197,7 +1287,7 @@
     <xdr:ext cx="1005840" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3" descr="{{image:red}}"/>
+        <xdr:cNvPr id="3" name="Picture 3" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1228,7 +1318,7 @@
     <xdr:ext cx="1051560" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="4" name="Picture 4" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1259,7 +1349,7 @@
     <xdr:ext cx="1097280" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5" descr="{{image:red}}"/>
+        <xdr:cNvPr id="5" name="Picture 5" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1290,7 +1380,7 @@
     <xdr:ext cx="1143000" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="6" name="Picture 6" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1321,7 +1411,7 @@
     <xdr:ext cx="1188720" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7" descr="{{image:red}}"/>
+        <xdr:cNvPr id="7" name="Picture 7" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1352,7 +1442,7 @@
     <xdr:ext cx="1234440" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="8" name="Picture 8" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1383,7 +1473,7 @@
     <xdr:ext cx="1280160" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9" descr="{{image:red}}"/>
+        <xdr:cNvPr id="9" name="Picture 9" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1414,7 +1504,7 @@
     <xdr:ext cx="1325880" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="10" name="Picture 10" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1440,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1767,10 +1857,10 @@
         <f>B40*C40</f>
         <v>0</v>
       </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{/each}}</t>
-        </is>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1797,7 +1887,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
